--- a/create_forecast_basic/utils/monitoring_df_fixed_2.xlsx
+++ b/create_forecast_basic/utils/monitoring_df_fixed_2.xlsx
@@ -508,22 +508,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>414,959</t>
+          <t>360,613</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>414,959</t>
+          <t>360,613</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>414,959</t>
+          <t>360,613</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>414,959</t>
+          <t>360,613</t>
         </is>
       </c>
     </row>
@@ -1010,13 +1010,13 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>10.46117968702283</v>
+        <v>10.46117968702281</v>
       </c>
       <c r="D28" t="n">
         <v>9.297933647380905</v>
       </c>
       <c r="E28" t="n">
-        <v>10.40351957662375</v>
+        <v>10.40351957662376</v>
       </c>
     </row>
     <row r="29">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>9.975617699839043</v>
+        <v>9.975617699839059</v>
       </c>
       <c r="D29" t="n">
         <v>8.601978752992911</v>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>9.051601597594949</v>
+        <v>9.051601597594933</v>
       </c>
       <c r="D30" t="n">
         <v>7.611918043502031</v>
@@ -1067,7 +1067,7 @@
         <v>6.827201862124387</v>
       </c>
       <c r="E31" t="n">
-        <v>8.165655199075662</v>
+        <v>8.165655199075676</v>
       </c>
     </row>
     <row r="32">
@@ -1081,10 +1081,10 @@
         <v>5.62802494006268</v>
       </c>
       <c r="D32" t="n">
-        <v>6.821126836812724</v>
+        <v>6.82112683681271</v>
       </c>
       <c r="E32" t="n">
-        <v>8.123887888276622</v>
+        <v>8.123887888276608</v>
       </c>
     </row>
     <row r="33">
@@ -20417,13 +20417,13 @@
       </c>
       <c r="B1168" t="inlineStr"/>
       <c r="C1168" t="n">
-        <v>9086.914285714285</v>
+        <v>8601.771428571428</v>
       </c>
       <c r="D1168" t="n">
-        <v>9086.914285714285</v>
+        <v>8601.771428571428</v>
       </c>
       <c r="E1168" t="n">
-        <v>9086.914285714285</v>
+        <v>8601.771428571428</v>
       </c>
     </row>
     <row r="1169">
@@ -20536,13 +20536,13 @@
       </c>
       <c r="B1175" t="inlineStr"/>
       <c r="C1175" t="n">
-        <v>972.52400255109</v>
+        <v>810.589936617024</v>
       </c>
       <c r="D1175" t="n">
-        <v>972.52400255109</v>
+        <v>810.589936617024</v>
       </c>
       <c r="E1175" t="n">
-        <v>972.52400255109</v>
+        <v>810.589936617024</v>
       </c>
     </row>
     <row r="1176">
@@ -20655,13 +20655,13 @@
       </c>
       <c r="B1182" t="inlineStr"/>
       <c r="C1182" t="n">
-        <v>978.0505494505495</v>
+        <v>714.3142857142857</v>
       </c>
       <c r="D1182" t="n">
-        <v>978.0505494505495</v>
+        <v>714.3142857142857</v>
       </c>
       <c r="E1182" t="n">
-        <v>978.0505494505495</v>
+        <v>714.3142857142857</v>
       </c>
     </row>
     <row r="1183">
@@ -20774,13 +20774,13 @@
       </c>
       <c r="B1189" t="inlineStr"/>
       <c r="C1189" t="n">
-        <v>789.7648351648352</v>
+        <v>616.8857142857144</v>
       </c>
       <c r="D1189" t="n">
-        <v>789.7648351648352</v>
+        <v>616.8857142857144</v>
       </c>
       <c r="E1189" t="n">
-        <v>789.7648351648352</v>
+        <v>616.8857142857144</v>
       </c>
     </row>
     <row r="1190">
@@ -20893,13 +20893,13 @@
       </c>
       <c r="B1196" t="inlineStr"/>
       <c r="C1196" t="n">
-        <v>1500.010989010989</v>
+        <v>1037.285714285714</v>
       </c>
       <c r="D1196" t="n">
-        <v>1500.010989010989</v>
+        <v>1037.285714285714</v>
       </c>
       <c r="E1196" t="n">
-        <v>1500.010989010989</v>
+        <v>1037.285714285714</v>
       </c>
     </row>
     <row r="1197">
@@ -21012,13 +21012,13 @@
       </c>
       <c r="B1203" t="inlineStr"/>
       <c r="C1203" t="n">
-        <v>4484.8</v>
+        <v>4064.8</v>
       </c>
       <c r="D1203" t="n">
-        <v>4484.8</v>
+        <v>4064.8</v>
       </c>
       <c r="E1203" t="n">
-        <v>4484.8</v>
+        <v>4064.8</v>
       </c>
     </row>
     <row r="1204">
@@ -21131,13 +21131,13 @@
       </c>
       <c r="B1210" t="inlineStr"/>
       <c r="C1210" t="n">
-        <v>881.3890109890109</v>
+        <v>588.1142857142858</v>
       </c>
       <c r="D1210" t="n">
-        <v>881.3890109890109</v>
+        <v>588.1142857142858</v>
       </c>
       <c r="E1210" t="n">
-        <v>881.3890109890109</v>
+        <v>588.1142857142858</v>
       </c>
     </row>
     <row r="1211">
@@ -21250,13 +21250,13 @@
       </c>
       <c r="B1217" t="inlineStr"/>
       <c r="C1217" t="n">
-        <v>475.0675824175825</v>
+        <v>375.5071428571429</v>
       </c>
       <c r="D1217" t="n">
-        <v>475.0675824175825</v>
+        <v>375.5071428571429</v>
       </c>
       <c r="E1217" t="n">
-        <v>475.0675824175825</v>
+        <v>375.5071428571429</v>
       </c>
     </row>
     <row r="1218">
@@ -21369,13 +21369,13 @@
       </c>
       <c r="B1224" t="inlineStr"/>
       <c r="C1224" t="n">
-        <v>23966.44079419275</v>
+        <v>18405.29793704989</v>
       </c>
       <c r="D1224" t="n">
-        <v>23966.44079419275</v>
+        <v>18405.29793704989</v>
       </c>
       <c r="E1224" t="n">
-        <v>23966.44079419275</v>
+        <v>18405.29793704989</v>
       </c>
     </row>
     <row r="1225">
@@ -21488,13 +21488,13 @@
       </c>
       <c r="B1231" t="inlineStr"/>
       <c r="C1231" t="n">
-        <v>8838.553729499759</v>
+        <v>6127.476806422837</v>
       </c>
       <c r="D1231" t="n">
-        <v>8838.553729499759</v>
+        <v>6127.476806422837</v>
       </c>
       <c r="E1231" t="n">
-        <v>8838.553729499759</v>
+        <v>6127.476806422837</v>
       </c>
     </row>
     <row r="1232">
@@ -21607,13 +21607,13 @@
       </c>
       <c r="B1238" t="inlineStr"/>
       <c r="C1238" t="n">
-        <v>1294.643956043956</v>
+        <v>1147.742857142857</v>
       </c>
       <c r="D1238" t="n">
-        <v>1294.643956043956</v>
+        <v>1147.742857142857</v>
       </c>
       <c r="E1238" t="n">
-        <v>1294.643956043956</v>
+        <v>1147.742857142857</v>
       </c>
     </row>
     <row r="1239">
@@ -21726,13 +21726,13 @@
       </c>
       <c r="B1245" t="inlineStr"/>
       <c r="C1245" t="n">
-        <v>3851.937362637363</v>
+        <v>3113.871428571429</v>
       </c>
       <c r="D1245" t="n">
-        <v>3851.937362637363</v>
+        <v>3113.871428571429</v>
       </c>
       <c r="E1245" t="n">
-        <v>3851.937362637363</v>
+        <v>3113.871428571429</v>
       </c>
     </row>
     <row r="1246">
@@ -21845,13 +21845,13 @@
       </c>
       <c r="B1252" t="inlineStr"/>
       <c r="C1252" t="n">
-        <v>324.523076923077</v>
+        <v>280.7428571428572</v>
       </c>
       <c r="D1252" t="n">
-        <v>324.523076923077</v>
+        <v>280.7428571428572</v>
       </c>
       <c r="E1252" t="n">
-        <v>324.523076923077</v>
+        <v>280.7428571428572</v>
       </c>
     </row>
     <row r="1253">
@@ -21965,13 +21965,13 @@
       </c>
       <c r="B1259" t="inlineStr"/>
       <c r="C1259" t="n">
-        <v>1061.164835164835</v>
+        <v>756.2857142857144</v>
       </c>
       <c r="D1259" t="n">
-        <v>1061.164835164835</v>
+        <v>756.2857142857144</v>
       </c>
       <c r="E1259" t="n">
-        <v>1061.164835164835</v>
+        <v>756.2857142857144</v>
       </c>
     </row>
     <row r="1260">
@@ -22090,13 +22090,13 @@
       </c>
       <c r="B1266" t="inlineStr"/>
       <c r="C1266" t="n">
-        <v>289605.1632852078</v>
+        <v>261333.6468016913</v>
       </c>
       <c r="D1266" t="n">
-        <v>289605.1632852078</v>
+        <v>261333.6468016913</v>
       </c>
       <c r="E1266" t="n">
-        <v>289605.1632852078</v>
+        <v>261333.6468016913</v>
       </c>
     </row>
     <row r="1267">
@@ -22209,13 +22209,13 @@
       </c>
       <c r="B1273" t="inlineStr"/>
       <c r="C1273" t="n">
-        <v>3499.297002362004</v>
+        <v>2979.209090274092</v>
       </c>
       <c r="D1273" t="n">
-        <v>3499.297002362004</v>
+        <v>2979.209090274092</v>
       </c>
       <c r="E1273" t="n">
-        <v>3499.297002362004</v>
+        <v>2979.209090274092</v>
       </c>
     </row>
     <row r="1274">
@@ -22329,13 +22329,13 @@
       </c>
       <c r="B1280" t="inlineStr"/>
       <c r="C1280" t="n">
-        <v>126.7516483516484</v>
+        <v>91.54285714285714</v>
       </c>
       <c r="D1280" t="n">
-        <v>126.7516483516484</v>
+        <v>91.54285714285714</v>
       </c>
       <c r="E1280" t="n">
-        <v>126.7516483516484</v>
+        <v>91.54285714285714</v>
       </c>
     </row>
     <row r="1281">
@@ -22454,13 +22454,13 @@
       </c>
       <c r="B1287" t="inlineStr"/>
       <c r="C1287" t="n">
-        <v>17586.54285714286</v>
+        <v>14607.11428571428</v>
       </c>
       <c r="D1287" t="n">
-        <v>17586.54285714286</v>
+        <v>14607.11428571428</v>
       </c>
       <c r="E1287" t="n">
-        <v>17586.54285714286</v>
+        <v>14607.11428571428</v>
       </c>
     </row>
     <row r="1288">
@@ -22573,13 +22573,13 @@
       </c>
       <c r="B1294" t="inlineStr"/>
       <c r="C1294" t="n">
-        <v>10948.60586486006</v>
+        <v>7507.506963761155</v>
       </c>
       <c r="D1294" t="n">
-        <v>10948.60586486006</v>
+        <v>7507.506963761155</v>
       </c>
       <c r="E1294" t="n">
-        <v>10948.60586486006</v>
+        <v>7507.506963761155</v>
       </c>
     </row>
     <row r="1295">
@@ -22692,13 +22692,13 @@
       </c>
       <c r="B1301" t="inlineStr"/>
       <c r="C1301" t="n">
-        <v>9407.521372100504</v>
+        <v>6983.1257677049</v>
       </c>
       <c r="D1301" t="n">
-        <v>9407.521372100504</v>
+        <v>6983.1257677049</v>
       </c>
       <c r="E1301" t="n">
-        <v>9407.521372100504</v>
+        <v>6983.1257677049</v>
       </c>
     </row>
     <row r="1302">
@@ -22811,13 +22811,13 @@
       </c>
       <c r="B1308" t="inlineStr"/>
       <c r="C1308" t="n">
-        <v>9933.892257445163</v>
+        <v>8819.342806895711</v>
       </c>
       <c r="D1308" t="n">
-        <v>9933.892257445163</v>
+        <v>8819.342806895711</v>
       </c>
       <c r="E1308" t="n">
-        <v>9933.892257445163</v>
+        <v>8819.342806895711</v>
       </c>
     </row>
     <row r="1309">
@@ -22930,13 +22930,13 @@
       </c>
       <c r="B1315" t="inlineStr"/>
       <c r="C1315" t="n">
-        <v>5371.879514269281</v>
+        <v>4387.22017360994</v>
       </c>
       <c r="D1315" t="n">
-        <v>5371.879514269281</v>
+        <v>4387.22017360994</v>
       </c>
       <c r="E1315" t="n">
-        <v>5371.879514269281</v>
+        <v>4387.22017360994</v>
       </c>
     </row>
     <row r="1316">
@@ -23049,13 +23049,13 @@
       </c>
       <c r="B1322" t="inlineStr"/>
       <c r="C1322" t="n">
-        <v>176.8175824175824</v>
+        <v>137.2571428571429</v>
       </c>
       <c r="D1322" t="n">
-        <v>176.8175824175824</v>
+        <v>137.2571428571429</v>
       </c>
       <c r="E1322" t="n">
-        <v>176.8175824175824</v>
+        <v>137.2571428571429</v>
       </c>
     </row>
     <row r="1323">
@@ -23168,13 +23168,13 @@
       </c>
       <c r="B1329" t="inlineStr"/>
       <c r="C1329" t="n">
-        <v>561.1274725274725</v>
+        <v>454.3142857142857</v>
       </c>
       <c r="D1329" t="n">
-        <v>561.1274725274725</v>
+        <v>454.3142857142857</v>
       </c>
       <c r="E1329" t="n">
-        <v>561.1274725274725</v>
+        <v>454.3142857142857</v>
       </c>
     </row>
     <row r="1330">
@@ -23288,13 +23288,13 @@
       </c>
       <c r="B1336" t="inlineStr"/>
       <c r="C1336" t="n">
-        <v>587.0571428571429</v>
+        <v>422.4857142857142</v>
       </c>
       <c r="D1336" t="n">
-        <v>587.0571428571429</v>
+        <v>422.4857142857142</v>
       </c>
       <c r="E1336" t="n">
-        <v>587.0571428571429</v>
+        <v>422.4857142857142</v>
       </c>
     </row>
     <row r="1337">
@@ -23413,13 +23413,13 @@
       </c>
       <c r="B1343" t="inlineStr"/>
       <c r="C1343" t="n">
-        <v>1151.369230769231</v>
+        <v>944.6</v>
       </c>
       <c r="D1343" t="n">
-        <v>1151.369230769231</v>
+        <v>944.6</v>
       </c>
       <c r="E1343" t="n">
-        <v>1151.369230769231</v>
+        <v>944.6</v>
       </c>
     </row>
     <row r="1344">
@@ -23532,13 +23532,13 @@
       </c>
       <c r="B1350" t="inlineStr"/>
       <c r="C1350" t="n">
-        <v>1074.615384615385</v>
+        <v>758</v>
       </c>
       <c r="D1350" t="n">
-        <v>1074.615384615385</v>
+        <v>758</v>
       </c>
       <c r="E1350" t="n">
-        <v>1074.615384615385</v>
+        <v>758</v>
       </c>
     </row>
     <row r="1351">
@@ -23651,13 +23651,13 @@
       </c>
       <c r="B1357" t="inlineStr"/>
       <c r="C1357" t="n">
-        <v>757.3210523939651</v>
+        <v>568.8814919544046</v>
       </c>
       <c r="D1357" t="n">
-        <v>757.3210523939651</v>
+        <v>568.8814919544046</v>
       </c>
       <c r="E1357" t="n">
-        <v>757.3210523939651</v>
+        <v>568.8814919544046</v>
       </c>
     </row>
     <row r="1358">
@@ -23770,13 +23770,13 @@
       </c>
       <c r="B1364" t="inlineStr"/>
       <c r="C1364" t="n">
-        <v>1210.936263736264</v>
+        <v>880.3428571428572</v>
       </c>
       <c r="D1364" t="n">
-        <v>1210.936263736264</v>
+        <v>880.3428571428572</v>
       </c>
       <c r="E1364" t="n">
-        <v>1210.936263736264</v>
+        <v>880.3428571428572</v>
       </c>
     </row>
     <row r="1365">
@@ -23889,13 +23889,13 @@
       </c>
       <c r="B1371" t="inlineStr"/>
       <c r="C1371" t="n">
-        <v>4454.698901098901</v>
+        <v>3098.171428571429</v>
       </c>
       <c r="D1371" t="n">
-        <v>4454.698901098901</v>
+        <v>3098.171428571429</v>
       </c>
       <c r="E1371" t="n">
-        <v>4454.698901098901</v>
+        <v>3098.171428571429</v>
       </c>
     </row>
     <row r="1372">
@@ -25912,13 +25912,13 @@
       </c>
       <c r="B1490" t="inlineStr"/>
       <c r="C1490" t="n">
-        <v>0.2359786867707097</v>
+        <v>0.2050732952712294</v>
       </c>
       <c r="D1490" t="n">
-        <v>0.2359786867707097</v>
+        <v>0.2050732952712294</v>
       </c>
       <c r="E1490" t="n">
-        <v>0.2359786867707097</v>
+        <v>0.2050732952712294</v>
       </c>
     </row>
     <row r="1491">
@@ -25929,13 +25929,13 @@
       </c>
       <c r="B1491" t="inlineStr"/>
       <c r="C1491" t="n">
-        <v>0.08584969999091832</v>
+        <v>0.08584969999091831</v>
       </c>
       <c r="D1491" t="n">
         <v>0.08879780740812651</v>
       </c>
       <c r="E1491" t="n">
-        <v>0.08953461815418942</v>
+        <v>0.08953461815418944</v>
       </c>
     </row>
     <row r="1492">
@@ -25963,7 +25963,7 @@
       </c>
       <c r="B1493" t="inlineStr"/>
       <c r="C1493" t="n">
-        <v>0.09982040824562943</v>
+        <v>0.09982040824562942</v>
       </c>
       <c r="D1493" t="n">
         <v>0.09284669531719444</v>
@@ -25983,7 +25983,7 @@
         <v>0.1046945184712901</v>
       </c>
       <c r="D1494" t="n">
-        <v>0.09479619891909367</v>
+        <v>0.09479619891909369</v>
       </c>
       <c r="E1494" t="n">
         <v>0.09946075859961466</v>
@@ -26031,13 +26031,13 @@
       </c>
       <c r="B1497" t="inlineStr"/>
       <c r="C1497" t="n">
-        <v>0.9577005906449759</v>
+        <v>0.832273535777408</v>
       </c>
       <c r="D1497" t="n">
-        <v>0.9577005906449759</v>
+        <v>0.832273535777408</v>
       </c>
       <c r="E1497" t="n">
-        <v>0.9577005906449759</v>
+        <v>0.832273535777408</v>
       </c>
     </row>
     <row r="1498">
@@ -26150,13 +26150,13 @@
       </c>
       <c r="B1504" t="inlineStr"/>
       <c r="C1504" t="n">
-        <v>-6.458689212799072</v>
+        <v>59.44718170166016</v>
       </c>
       <c r="D1504" t="n">
-        <v>-7.93978214263916</v>
+        <v>56.92256164550781</v>
       </c>
       <c r="E1504" t="n">
-        <v>-5.291823387145996</v>
+        <v>61.43617630004883</v>
       </c>
     </row>
     <row r="1505">
@@ -26167,13 +26167,13 @@
       </c>
       <c r="B1505" t="inlineStr"/>
       <c r="C1505" t="n">
-        <v>-32.00569534301758</v>
+        <v>30.75827980041504</v>
       </c>
       <c r="D1505" t="n">
-        <v>-32.0456657409668</v>
+        <v>30.68141555786133</v>
       </c>
       <c r="E1505" t="n">
-        <v>-31.86953926086426</v>
+        <v>31.02011489868164</v>
       </c>
     </row>
     <row r="1506">
@@ -26184,13 +26184,13 @@
       </c>
       <c r="B1506" t="inlineStr"/>
       <c r="C1506" t="n">
-        <v>-28.84376525878906</v>
+        <v>36.83891296386719</v>
       </c>
       <c r="D1506" t="n">
-        <v>-29.46407127380371</v>
+        <v>35.64601898193359</v>
       </c>
       <c r="E1506" t="n">
-        <v>-29.19508934020996</v>
+        <v>36.16329193115234</v>
       </c>
     </row>
     <row r="1507">
@@ -26201,13 +26201,13 @@
       </c>
       <c r="B1507" t="inlineStr"/>
       <c r="C1507" t="n">
-        <v>2.556742668151855</v>
+        <v>6.925570011138916</v>
       </c>
       <c r="D1507" t="n">
-        <v>1.744897723197937</v>
+        <v>6.079141139984131</v>
       </c>
       <c r="E1507" t="n">
-        <v>3.471516609191895</v>
+        <v>7.879312515258789</v>
       </c>
     </row>
     <row r="1508">
@@ -26218,13 +26218,13 @@
       </c>
       <c r="B1508" t="inlineStr"/>
       <c r="C1508" t="n">
-        <v>-48</v>
+        <v>0</v>
       </c>
       <c r="D1508" t="n">
-        <v>-48</v>
+        <v>0</v>
       </c>
       <c r="E1508" t="n">
-        <v>-48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1509">
@@ -26235,13 +26235,13 @@
       </c>
       <c r="B1509" t="inlineStr"/>
       <c r="C1509" t="n">
-        <v>-3.131037473678589</v>
+        <v>17.44314002990723</v>
       </c>
       <c r="D1509" t="n">
-        <v>-7.790164947509766</v>
+        <v>11.7944507598877</v>
       </c>
       <c r="E1509" t="n">
-        <v>-4.416707038879395</v>
+        <v>15.88440418243408</v>
       </c>
     </row>
     <row r="1510">
@@ -26252,13 +26252,13 @@
       </c>
       <c r="B1510" t="inlineStr"/>
       <c r="C1510" t="n">
-        <v>-35.94775009155273</v>
+        <v>23.17740249633789</v>
       </c>
       <c r="D1510" t="n">
-        <v>-36.17729187011719</v>
+        <v>22.73597717285156</v>
       </c>
       <c r="E1510" t="n">
-        <v>-36.06415939331055</v>
+        <v>22.95353889465332</v>
       </c>
     </row>
     <row r="1511">
@@ -26269,13 +26269,13 @@
       </c>
       <c r="B1511" t="inlineStr"/>
       <c r="C1511" t="n">
-        <v>-28.5030689239502</v>
+        <v>14.72390842437744</v>
       </c>
       <c r="D1511" t="n">
-        <v>-31.02093696594238</v>
+        <v>10.68373966217041</v>
       </c>
       <c r="E1511" t="n">
-        <v>-29.28396224975586</v>
+        <v>13.47088623046875</v>
       </c>
     </row>
     <row r="1512">
@@ -26297,13 +26297,13 @@
       </c>
       <c r="B1513" t="inlineStr"/>
       <c r="C1513" t="n">
-        <v>-18.57325172424316</v>
+        <v>56.58990097045898</v>
       </c>
       <c r="D1513" t="n">
-        <v>-20.67618560791016</v>
+        <v>52.54579925537109</v>
       </c>
       <c r="E1513" t="n">
-        <v>-18.5692310333252</v>
+        <v>56.59763336181641</v>
       </c>
     </row>
     <row r="1514">
@@ -26314,13 +26314,13 @@
       </c>
       <c r="B1514" t="inlineStr"/>
       <c r="C1514" t="n">
-        <v>-9.211896896362305</v>
+        <v>72.17302703857422</v>
       </c>
       <c r="D1514" t="n">
-        <v>-13.7275972366333</v>
+        <v>63.60932922363281</v>
       </c>
       <c r="E1514" t="n">
-        <v>-10.88778305053711</v>
+        <v>68.99482727050781</v>
       </c>
     </row>
     <row r="1515">
@@ -26331,13 +26331,13 @@
       </c>
       <c r="B1515" t="inlineStr"/>
       <c r="C1515" t="n">
-        <v>-16.35707473754883</v>
+        <v>60.85177993774414</v>
       </c>
       <c r="D1515" t="n">
-        <v>-17.41849517822266</v>
+        <v>58.81058883666992</v>
       </c>
       <c r="E1515" t="n">
-        <v>-15.27130794525146</v>
+        <v>62.93979263305664</v>
       </c>
     </row>
     <row r="1516">
@@ -26348,13 +26348,13 @@
       </c>
       <c r="B1516" t="inlineStr"/>
       <c r="C1516" t="n">
-        <v>-26.01636695861816</v>
+        <v>32.90478515625</v>
       </c>
       <c r="D1516" t="n">
-        <v>-26.57264518737793</v>
+        <v>31.90548324584961</v>
       </c>
       <c r="E1516" t="n">
-        <v>-26.13095283508301</v>
+        <v>32.69894027709961</v>
       </c>
     </row>
     <row r="1517">
@@ -26365,13 +26365,13 @@
       </c>
       <c r="B1517" t="inlineStr"/>
       <c r="C1517" t="n">
-        <v>-26.24299240112305</v>
+        <v>21.37066459655762</v>
       </c>
       <c r="D1517" t="n">
-        <v>-29.22551345825195</v>
+        <v>16.4627857208252</v>
       </c>
       <c r="E1517" t="n">
-        <v>-29.17081642150879</v>
+        <v>16.55279159545898</v>
       </c>
     </row>
     <row r="1518">
@@ -26416,13 +26416,13 @@
       </c>
       <c r="B1520" t="inlineStr"/>
       <c r="C1520" t="n">
-        <v>-31.09913063049316</v>
+        <v>18.31140899658203</v>
       </c>
       <c r="D1520" t="n">
-        <v>-36.09987258911133</v>
+        <v>9.724510192871094</v>
       </c>
       <c r="E1520" t="n">
-        <v>-36.45967102050781</v>
+        <v>9.106692314147949</v>
       </c>
     </row>
     <row r="1521">
@@ -26433,13 +26433,13 @@
       </c>
       <c r="B1521" t="inlineStr"/>
       <c r="C1521" t="n">
-        <v>-10.5558385848999</v>
+        <v>66.94136047363281</v>
       </c>
       <c r="D1521" t="n">
-        <v>-12.36332607269287</v>
+        <v>63.56780624389648</v>
       </c>
       <c r="E1521" t="n">
-        <v>-9.896894454956055</v>
+        <v>68.17123413085938</v>
       </c>
     </row>
     <row r="1522">
@@ -26461,13 +26461,13 @@
       </c>
       <c r="B1523" t="inlineStr"/>
       <c r="C1523" t="n">
-        <v>-21.18726348876953</v>
+        <v>25.46394920349121</v>
       </c>
       <c r="D1523" t="n">
-        <v>-24.66475296020508</v>
+        <v>19.92804527282715</v>
       </c>
       <c r="E1523" t="n">
-        <v>-22.92583274841309</v>
+        <v>22.69627571105957</v>
       </c>
     </row>
     <row r="1524">
@@ -26478,13 +26478,13 @@
       </c>
       <c r="B1524" t="inlineStr"/>
       <c r="C1524" t="n">
-        <v>0.05418065935373306</v>
+        <v>87.08224487304688</v>
       </c>
       <c r="D1524" t="n">
-        <v>-6.902203559875488</v>
+        <v>74.07513427734375</v>
       </c>
       <c r="E1524" t="n">
-        <v>-3.36484432220459</v>
+        <v>80.68931579589844</v>
       </c>
     </row>
     <row r="1525">
@@ -26518,13 +26518,13 @@
       </c>
       <c r="B1526" t="inlineStr"/>
       <c r="C1526" t="n">
-        <v>-6.540797233581543</v>
+        <v>3.360461711883545</v>
       </c>
       <c r="D1526" t="n">
-        <v>-7.363945007324219</v>
+        <v>2.450108051300049</v>
       </c>
       <c r="E1526" t="n">
-        <v>-6.30854606628418</v>
+        <v>3.617317676544189</v>
       </c>
     </row>
     <row r="1527">
@@ -26535,13 +26535,13 @@
       </c>
       <c r="B1527" t="inlineStr"/>
       <c r="C1527" t="n">
-        <v>-9.065347671508789</v>
+        <v>74.87432861328125</v>
       </c>
       <c r="D1527" t="n">
-        <v>-9.53482723236084</v>
+        <v>73.97148895263672</v>
       </c>
       <c r="E1527" t="n">
-        <v>-9.130251884460449</v>
+        <v>74.74951171875</v>
       </c>
     </row>
     <row r="1528">
@@ -26552,13 +26552,13 @@
       </c>
       <c r="B1528" t="inlineStr"/>
       <c r="C1528" t="n">
-        <v>-5.304049968719482</v>
+        <v>21.04438591003418</v>
       </c>
       <c r="D1528" t="n">
-        <v>-11.00427436828613</v>
+        <v>13.75811767578125</v>
       </c>
       <c r="E1528" t="n">
-        <v>-11.18592834472656</v>
+        <v>13.52591896057129</v>
       </c>
     </row>
     <row r="1529">
@@ -26569,13 +26569,13 @@
       </c>
       <c r="B1529" t="inlineStr"/>
       <c r="C1529" t="n">
-        <v>57.56622695922852</v>
+        <v>203.0119781494141</v>
       </c>
       <c r="D1529" t="n">
-        <v>54.45578002929688</v>
+        <v>197.0303497314453</v>
       </c>
       <c r="E1529" t="n">
-        <v>55.47430038452148</v>
+        <v>198.9890441894531</v>
       </c>
     </row>
     <row r="1530">
@@ -26586,13 +26586,13 @@
       </c>
       <c r="B1530" t="inlineStr"/>
       <c r="C1530" t="n">
-        <v>-3.73189115524292</v>
+        <v>42.62131881713867</v>
       </c>
       <c r="D1530" t="n">
-        <v>-6.02564811706543</v>
+        <v>39.22311401367188</v>
       </c>
       <c r="E1530" t="n">
-        <v>-3.186822652816772</v>
+        <v>43.42883682250977</v>
       </c>
     </row>
     <row r="1531">
@@ -26603,13 +26603,13 @@
       </c>
       <c r="B1531" t="inlineStr"/>
       <c r="C1531" t="n">
-        <v>-29.31197166442871</v>
+        <v>17.97091484069824</v>
       </c>
       <c r="D1531" t="n">
-        <v>-30.58390998840332</v>
+        <v>15.84818363189697</v>
       </c>
       <c r="E1531" t="n">
-        <v>-30.23233985900879</v>
+        <v>16.43491554260254</v>
       </c>
     </row>
     <row r="1532">
@@ -26620,13 +26620,13 @@
       </c>
       <c r="B1532" t="inlineStr"/>
       <c r="C1532" t="n">
-        <v>-3.915107488632202</v>
+        <v>30.31511878967285</v>
       </c>
       <c r="D1532" t="n">
-        <v>-8.884498596191406</v>
+        <v>23.57538414001465</v>
       </c>
       <c r="E1532" t="n">
-        <v>-6.258064270019531</v>
+        <v>27.13748359680176</v>
       </c>
     </row>
     <row r="1533">
@@ -26637,13 +26637,13 @@
       </c>
       <c r="B1533" t="inlineStr"/>
       <c r="C1533" t="n">
-        <v>-22.16257095336914</v>
+        <v>25.92532348632812</v>
       </c>
       <c r="D1533" t="n">
-        <v>-26.55992126464844</v>
+        <v>18.81129455566406</v>
       </c>
       <c r="E1533" t="n">
-        <v>-26.39327430725098</v>
+        <v>19.08089447021484</v>
       </c>
     </row>
     <row r="1534">
@@ -26654,13 +26654,13 @@
       </c>
       <c r="B1534" t="inlineStr"/>
       <c r="C1534" t="n">
-        <v>-38.67049789428711</v>
+        <v>17.82489013671875</v>
       </c>
       <c r="D1534" t="n">
-        <v>-38.77999496459961</v>
+        <v>17.61452865600586</v>
       </c>
       <c r="E1534" t="n">
-        <v>-38.68926239013672</v>
+        <v>17.78883934020996</v>
       </c>
     </row>
     <row r="1535">
@@ -26671,13 +26671,13 @@
       </c>
       <c r="B1535" t="inlineStr"/>
       <c r="C1535" t="n">
-        <v>-39.44704818725586</v>
+        <v>6.288867473602295</v>
       </c>
       <c r="D1535" t="n">
-        <v>-39.2588996887207</v>
+        <v>6.619128227233887</v>
       </c>
       <c r="E1535" t="n">
-        <v>-39.01197052001953</v>
+        <v>7.052563667297363</v>
       </c>
     </row>
     <row r="1536">
@@ -26705,13 +26705,13 @@
       </c>
       <c r="B1537" t="inlineStr"/>
       <c r="C1537" t="n">
-        <v>-29.41322326660156</v>
+        <v>33.48637008666992</v>
       </c>
       <c r="D1537" t="n">
-        <v>-35.62997055053711</v>
+        <v>21.72990608215332</v>
       </c>
       <c r="E1537" t="n">
-        <v>-36.37380599975586</v>
+        <v>20.32324028015137</v>
       </c>
     </row>
     <row r="1538">
@@ -26722,13 +26722,13 @@
       </c>
       <c r="B1538" t="inlineStr"/>
       <c r="C1538" t="n">
-        <v>9.314525604248047</v>
+        <v>28.27636528015137</v>
       </c>
       <c r="D1538" t="n">
-        <v>3.964420080184937</v>
+        <v>21.99822425842285</v>
       </c>
       <c r="E1538" t="n">
-        <v>5.96070671081543</v>
+        <v>24.34078788757324</v>
       </c>
     </row>
     <row r="1539">
@@ -26739,13 +26739,13 @@
       </c>
       <c r="B1539" t="inlineStr"/>
       <c r="C1539" t="n">
-        <v>-32.07715225219727</v>
+        <v>17.6546630859375</v>
       </c>
       <c r="D1539" t="n">
-        <v>-35.19334411621094</v>
+        <v>12.25685787200928</v>
       </c>
       <c r="E1539" t="n">
-        <v>-34.30155563354492</v>
+        <v>13.80159282684326</v>
       </c>
     </row>
     <row r="1540">
@@ -26756,13 +26756,13 @@
       </c>
       <c r="B1540" t="inlineStr"/>
       <c r="C1540" t="n">
-        <v>-33.05783462524414</v>
+        <v>22.25003814697266</v>
       </c>
       <c r="D1540" t="n">
-        <v>-37.58584213256836</v>
+        <v>13.98097133636475</v>
       </c>
       <c r="E1540" t="n">
-        <v>-37.75868988037109</v>
+        <v>13.66531467437744</v>
       </c>
     </row>
     <row r="1541">
@@ -26773,13 +26773,13 @@
       </c>
       <c r="B1541" t="inlineStr"/>
       <c r="C1541" t="n">
-        <v>76.52216339111328</v>
+        <v>239.4656982421875</v>
       </c>
       <c r="D1541" t="n">
-        <v>55.1190299987793</v>
+        <v>198.3058319091797</v>
       </c>
       <c r="E1541" t="n">
-        <v>64.63491821289062</v>
+        <v>216.6056213378906</v>
       </c>
     </row>
     <row r="1542">
@@ -26790,13 +26790,13 @@
       </c>
       <c r="B1542" t="inlineStr"/>
       <c r="C1542" t="n">
-        <v>-35.14753723144531</v>
+        <v>24.71627235412598</v>
       </c>
       <c r="D1542" t="n">
-        <v>-35.20293045043945</v>
+        <v>24.6097526550293</v>
       </c>
       <c r="E1542" t="n">
-        <v>-35.05650329589844</v>
+        <v>24.89133834838867</v>
       </c>
     </row>
     <row r="1543">
@@ -26807,13 +26807,13 @@
       </c>
       <c r="B1543" t="inlineStr"/>
       <c r="C1543" t="n">
-        <v>-0.1596934944391251</v>
+        <v>90.55043029785156</v>
       </c>
       <c r="D1543" t="n">
-        <v>-5.341487407684326</v>
+        <v>80.66070556640625</v>
       </c>
       <c r="E1543" t="n">
-        <v>-2.033071756362915</v>
+        <v>86.97499084472656</v>
       </c>
     </row>
     <row r="1544">
@@ -26824,13 +26824,13 @@
       </c>
       <c r="B1544" t="inlineStr"/>
       <c r="C1544" t="n">
-        <v>-36.70893096923828</v>
+        <v>20.81205558776855</v>
       </c>
       <c r="D1544" t="n">
-        <v>-39.07160949707031</v>
+        <v>16.30210494995117</v>
       </c>
       <c r="E1544" t="n">
-        <v>-38.08582305908203</v>
+        <v>18.18380165100098</v>
       </c>
     </row>
     <row r="1545">
@@ -26841,13 +26841,13 @@
       </c>
       <c r="B1545" t="inlineStr"/>
       <c r="C1545" t="n">
-        <v>-38.30388259887695</v>
+        <v>18.6463794708252</v>
       </c>
       <c r="D1545" t="n">
-        <v>-38.52179336547852</v>
+        <v>18.22731781005859</v>
       </c>
       <c r="E1545" t="n">
-        <v>-38.42876434326172</v>
+        <v>18.40622520446777</v>
       </c>
     </row>
     <row r="1546">
@@ -26858,13 +26858,13 @@
       </c>
       <c r="B1546" t="inlineStr"/>
       <c r="C1546" t="n">
-        <v>-31.73883247375488</v>
+        <v>31.27147674560547</v>
       </c>
       <c r="D1546" t="n">
-        <v>-35.13603591918945</v>
+        <v>24.73839378356934</v>
       </c>
       <c r="E1546" t="n">
-        <v>-33.77647018432617</v>
+        <v>27.35294342041016</v>
       </c>
     </row>
     <row r="1547">
@@ -26886,13 +26886,13 @@
       </c>
       <c r="B1548" t="inlineStr"/>
       <c r="C1548" t="n">
-        <v>-30.77907180786133</v>
+        <v>20.94045639038086</v>
       </c>
       <c r="D1548" t="n">
-        <v>-34.50428771972656</v>
+        <v>14.431884765625</v>
       </c>
       <c r="E1548" t="n">
-        <v>-34.20011520385742</v>
+        <v>14.96332931518555</v>
       </c>
     </row>
     <row r="1549">
@@ -26903,13 +26903,13 @@
       </c>
       <c r="B1549" t="inlineStr"/>
       <c r="C1549" t="n">
-        <v>-25.37919807434082</v>
+        <v>43.50154113769531</v>
       </c>
       <c r="D1549" t="n">
-        <v>-26.18971633911133</v>
+        <v>41.94285583496094</v>
       </c>
       <c r="E1549" t="n">
-        <v>-25.91293907165527</v>
+        <v>42.47512054443359</v>
       </c>
     </row>
     <row r="1550">
@@ -26931,13 +26931,13 @@
       </c>
       <c r="B1551" t="inlineStr"/>
       <c r="C1551" t="n">
-        <v>-31.9850902557373</v>
+        <v>23.0809268951416</v>
       </c>
       <c r="D1551" t="n">
-        <v>-35.74134826660156</v>
+        <v>16.28354263305664</v>
       </c>
       <c r="E1551" t="n">
-        <v>-35.83961486816406</v>
+        <v>16.105712890625</v>
       </c>
     </row>
     <row r="1552">
@@ -26948,13 +26948,13 @@
       </c>
       <c r="B1552" t="inlineStr"/>
       <c r="C1552" t="n">
-        <v>-14.41475296020508</v>
+        <v>53.16835784912109</v>
       </c>
       <c r="D1552" t="n">
-        <v>-23.85735893249512</v>
+        <v>36.26931762695312</v>
       </c>
       <c r="E1552" t="n">
-        <v>-24.89407348632812</v>
+        <v>34.4139518737793</v>
       </c>
     </row>
     <row r="1553">
@@ -26965,13 +26965,13 @@
       </c>
       <c r="B1553" t="inlineStr"/>
       <c r="C1553" t="n">
-        <v>-27.69198226928711</v>
+        <v>16.94012451171875</v>
       </c>
       <c r="D1553" t="n">
-        <v>-30.14647102355957</v>
+        <v>12.97060203552246</v>
       </c>
       <c r="E1553" t="n">
-        <v>-29.14835929870605</v>
+        <v>14.58480072021484</v>
       </c>
     </row>
     <row r="1554">
@@ -26982,13 +26982,13 @@
       </c>
       <c r="B1554" t="inlineStr"/>
       <c r="C1554" t="n">
-        <v>-15.74172115325928</v>
+        <v>54.46036148071289</v>
       </c>
       <c r="D1554" t="n">
-        <v>-21.2332878112793</v>
+        <v>44.39334487915039</v>
       </c>
       <c r="E1554" t="n">
-        <v>-18.85569763183594</v>
+        <v>48.75188827514648</v>
       </c>
     </row>
     <row r="1555">
@@ -26999,13 +26999,13 @@
       </c>
       <c r="B1555" t="inlineStr"/>
       <c r="C1555" t="n">
-        <v>-0.9745497703552246</v>
+        <v>90.43355560302734</v>
       </c>
       <c r="D1555" t="n">
-        <v>-11.40705108642578</v>
+        <v>70.37105560302734</v>
       </c>
       <c r="E1555" t="n">
-        <v>-12.34379768371582</v>
+        <v>68.56961822509766</v>
       </c>
     </row>
     <row r="1556">
@@ -27016,13 +27016,13 @@
       </c>
       <c r="B1556" t="inlineStr"/>
       <c r="C1556" t="n">
-        <v>-35.89145278930664</v>
+        <v>16.07633209228516</v>
       </c>
       <c r="D1556" t="n">
-        <v>-35.89864349365234</v>
+        <v>16.06331253051758</v>
       </c>
       <c r="E1556" t="n">
-        <v>-35.7598876953125</v>
+        <v>16.31454086303711</v>
       </c>
     </row>
     <row r="1557">
@@ -27033,13 +27033,13 @@
       </c>
       <c r="B1557" t="inlineStr"/>
       <c r="C1557" t="n">
-        <v>25.25138664245605</v>
+        <v>69.16249847412109</v>
       </c>
       <c r="D1557" t="n">
-        <v>20.23694801330566</v>
+        <v>62.39007949829102</v>
       </c>
       <c r="E1557" t="n">
-        <v>28.39867782592773</v>
+        <v>73.41318511962891</v>
       </c>
     </row>
     <row r="1558">
@@ -27050,13 +27050,13 @@
       </c>
       <c r="B1558" t="inlineStr"/>
       <c r="C1558" t="n">
-        <v>-7.869227886199951</v>
+        <v>61.93693161010742</v>
       </c>
       <c r="D1558" t="n">
-        <v>-15.23948192596436</v>
+        <v>48.98234176635742</v>
       </c>
       <c r="E1558" t="n">
-        <v>-11.89180564880371</v>
+        <v>54.86650466918945</v>
       </c>
     </row>
     <row r="1559">
@@ -27067,13 +27067,13 @@
       </c>
       <c r="B1559" t="inlineStr"/>
       <c r="C1559" t="n">
-        <v>-15.60618591308594</v>
+        <v>54.54816818237305</v>
       </c>
       <c r="D1559" t="n">
-        <v>-19.02043151855469</v>
+        <v>48.29574966430664</v>
       </c>
       <c r="E1559" t="n">
-        <v>-16.6761360168457</v>
+        <v>52.58879470825195</v>
       </c>
     </row>
     <row r="1560">
@@ -31812,13 +31812,13 @@
       </c>
       <c r="B1840" t="inlineStr"/>
       <c r="C1840" t="n">
-        <v>-8.940157890319824</v>
+        <v>75.11508178710938</v>
       </c>
       <c r="D1840" t="n">
-        <v>-10.28324222564697</v>
+        <v>72.5322265625</v>
       </c>
       <c r="E1840" t="n">
-        <v>-9.841169357299805</v>
+        <v>73.38236999511719</v>
       </c>
     </row>
     <row r="1841">
@@ -31829,13 +31829,13 @@
       </c>
       <c r="B1841" t="inlineStr"/>
       <c r="C1841" t="n">
-        <v>-28.45031547546387</v>
+        <v>37.59554672241211</v>
       </c>
       <c r="D1841" t="n">
-        <v>-25.7514762878418</v>
+        <v>42.78562164306641</v>
       </c>
       <c r="E1841" t="n">
-        <v>-25.2043285369873</v>
+        <v>43.83782958984375</v>
       </c>
     </row>
     <row r="1842">
@@ -31846,13 +31846,13 @@
       </c>
       <c r="B1842" t="inlineStr"/>
       <c r="C1842" t="n">
-        <v>27.62912940979004</v>
+        <v>144.8149261474609</v>
       </c>
       <c r="D1842" t="n">
-        <v>28.98475074768066</v>
+        <v>147.4152526855469</v>
       </c>
       <c r="E1842" t="n">
-        <v>30.40701866149902</v>
+        <v>150.1434020996094</v>
       </c>
     </row>
     <row r="1843">
@@ -31863,13 +31863,13 @@
       </c>
       <c r="B1843" t="inlineStr"/>
       <c r="C1843" t="n">
-        <v>-38.44715881347656</v>
+        <v>16.8271369934082</v>
       </c>
       <c r="D1843" t="n">
-        <v>-35.30134963989258</v>
+        <v>22.79787635803223</v>
       </c>
       <c r="E1843" t="n">
-        <v>-34.74662399291992</v>
+        <v>23.85074615478516</v>
       </c>
     </row>
     <row r="1844">
@@ -31880,13 +31880,13 @@
       </c>
       <c r="B1844" t="inlineStr"/>
       <c r="C1844" t="n">
-        <v>-3.21936559677124</v>
+        <v>10.50838375091553</v>
       </c>
       <c r="D1844" t="n">
-        <v>-4.038833618164062</v>
+        <v>9.57267951965332</v>
       </c>
       <c r="E1844" t="n">
-        <v>-1.283424019813538</v>
+        <v>12.71892738342285</v>
       </c>
     </row>
     <row r="1845">
@@ -31897,13 +31897,13 @@
       </c>
       <c r="B1845" t="inlineStr"/>
       <c r="C1845" t="n">
-        <v>-30.76418495178223</v>
+        <v>26.96766090393066</v>
       </c>
       <c r="D1845" t="n">
-        <v>-34.61318206787109</v>
+        <v>19.90920257568359</v>
       </c>
       <c r="E1845" t="n">
-        <v>-34.08663558959961</v>
+        <v>20.87480163574219</v>
       </c>
     </row>
     <row r="1846">
@@ -31914,13 +31914,13 @@
       </c>
       <c r="B1846" t="inlineStr"/>
       <c r="C1846" t="n">
-        <v>45.0267219543457</v>
+        <v>178.8975372314453</v>
       </c>
       <c r="D1846" t="n">
-        <v>33.20018005371094</v>
+        <v>156.1541900634766</v>
       </c>
       <c r="E1846" t="n">
-        <v>48.18932342529297</v>
+        <v>184.9794616699219</v>
       </c>
     </row>
     <row r="1847">
@@ -31931,13 +31931,13 @@
       </c>
       <c r="B1847" t="inlineStr"/>
       <c r="C1847" t="n">
-        <v>-26.64229202270508</v>
+        <v>38.16794967651367</v>
       </c>
       <c r="D1847" t="n">
-        <v>-31.61293411254883</v>
+        <v>28.80583190917969</v>
       </c>
       <c r="E1847" t="n">
-        <v>-29.40289115905762</v>
+        <v>32.96841049194336</v>
       </c>
     </row>
     <row r="1848">
@@ -31948,13 +31948,13 @@
       </c>
       <c r="B1848" t="inlineStr"/>
       <c r="C1848" t="n">
-        <v>-23.07664680480957</v>
+        <v>42.88733291625977</v>
       </c>
       <c r="D1848" t="n">
-        <v>-19.38433074951172</v>
+        <v>49.74591827392578</v>
       </c>
       <c r="E1848" t="n">
-        <v>-18.22805213928223</v>
+        <v>51.89374160766602</v>
       </c>
     </row>
     <row r="1849">
@@ -31965,13 +31965,13 @@
       </c>
       <c r="B1849" t="inlineStr"/>
       <c r="C1849" t="n">
-        <v>138.2331390380859</v>
+        <v>355.4113159179688</v>
       </c>
       <c r="D1849" t="n">
-        <v>162.4386138916016</v>
+        <v>401.6829833984375</v>
       </c>
       <c r="E1849" t="n">
-        <v>170.8627471923828</v>
+        <v>417.7867126464844</v>
       </c>
     </row>
     <row r="1850">
@@ -31982,13 +31982,13 @@
       </c>
       <c r="B1850" t="inlineStr"/>
       <c r="C1850" t="n">
-        <v>-9.551749229431152</v>
+        <v>37.01500701904297</v>
       </c>
       <c r="D1850" t="n">
-        <v>-10.37241840362549</v>
+        <v>35.77182388305664</v>
       </c>
       <c r="E1850" t="n">
-        <v>-8.964310646057129</v>
+        <v>37.90488815307617</v>
       </c>
     </row>
     <row r="1851">
@@ -31999,13 +31999,13 @@
       </c>
       <c r="B1851" t="inlineStr"/>
       <c r="C1851" t="n">
-        <v>43.4904670715332</v>
+        <v>175.9432067871094</v>
       </c>
       <c r="D1851" t="n">
-        <v>49.65402984619141</v>
+        <v>187.7962036132812</v>
       </c>
       <c r="E1851" t="n">
-        <v>53.30073547363281</v>
+        <v>194.8090972900391</v>
       </c>
     </row>
     <row r="1852">
@@ -32017,13 +32017,13 @@
       </c>
       <c r="B1852" t="inlineStr"/>
       <c r="C1852" t="n">
-        <v>-22.16069221496582</v>
+        <v>39.27460861206055</v>
       </c>
       <c r="D1852" t="n">
-        <v>-21.57657432556152</v>
+        <v>40.31974792480469</v>
       </c>
       <c r="E1852" t="n">
-        <v>-19.96999931335449</v>
+        <v>43.19432830810547</v>
       </c>
     </row>
     <row r="1853">
@@ -32034,13 +32034,13 @@
       </c>
       <c r="B1853" t="inlineStr"/>
       <c r="C1853" t="n">
-        <v>-21.80412101745605</v>
+        <v>26.28520965576172</v>
       </c>
       <c r="D1853" t="n">
-        <v>-24.29632949829102</v>
+        <v>22.26032829284668</v>
       </c>
       <c r="E1853" t="n">
-        <v>-23.4680347442627</v>
+        <v>23.5980110168457</v>
       </c>
     </row>
     <row r="1854">
@@ -32051,13 +32051,13 @@
       </c>
       <c r="B1854" t="inlineStr"/>
       <c r="C1854" t="n">
-        <v>-30.15028762817383</v>
+        <v>33.31263732910156</v>
       </c>
       <c r="D1854" t="n">
-        <v>-33.98865127563477</v>
+        <v>25.98687171936035</v>
       </c>
       <c r="E1854" t="n">
-        <v>-32.14559173583984</v>
+        <v>29.50446701049805</v>
       </c>
     </row>
     <row r="1855">
@@ -32069,13 +32069,13 @@
       </c>
       <c r="B1855" t="inlineStr"/>
       <c r="C1855" t="n">
-        <v>-15.99404907226562</v>
+        <v>61.54990386962891</v>
       </c>
       <c r="D1855" t="n">
-        <v>-12.52313041687012</v>
+        <v>68.22474670410156</v>
       </c>
       <c r="E1855" t="n">
-        <v>-11.20553302764893</v>
+        <v>70.75859069824219</v>
       </c>
     </row>
     <row r="1856">
@@ -32086,13 +32086,13 @@
       </c>
       <c r="B1856" t="inlineStr"/>
       <c r="C1856" t="n">
-        <v>-29.41009140014648</v>
+        <v>35.74982452392578</v>
       </c>
       <c r="D1856" t="n">
-        <v>-29.41009140014648</v>
+        <v>35.74982452392578</v>
       </c>
       <c r="E1856" t="n">
-        <v>-29.41009140014648</v>
+        <v>35.74982452392578</v>
       </c>
     </row>
     <row r="1857">
@@ -32103,13 +32103,13 @@
       </c>
       <c r="B1857" t="inlineStr"/>
       <c r="C1857" t="n">
-        <v>-25.99195861816406</v>
+        <v>36.58246994018555</v>
       </c>
       <c r="D1857" t="n">
-        <v>-22.63495254516602</v>
+        <v>42.77785491943359</v>
       </c>
       <c r="E1857" t="n">
-        <v>-20.26705169677734</v>
+        <v>47.14783477783203</v>
       </c>
     </row>
     <row r="1858">
@@ -32120,13 +32120,13 @@
       </c>
       <c r="B1858" t="inlineStr"/>
       <c r="C1858" t="n">
-        <v>-29.07699394226074</v>
+        <v>33.3934440612793</v>
       </c>
       <c r="D1858" t="n">
-        <v>-29.23058891296387</v>
+        <v>33.10456085205078</v>
       </c>
       <c r="E1858" t="n">
-        <v>-28.31185913085938</v>
+        <v>34.83252716064453</v>
       </c>
     </row>
     <row r="1859">
@@ -32137,13 +32137,13 @@
       </c>
       <c r="B1859" t="inlineStr"/>
       <c r="C1859" t="n">
-        <v>17.64059066772461</v>
+        <v>124.9872360229492</v>
       </c>
       <c r="D1859" t="n">
-        <v>8.361394882202148</v>
+        <v>107.2407989501953</v>
       </c>
       <c r="E1859" t="n">
-        <v>12.10616874694824</v>
+        <v>114.4026718139648</v>
       </c>
     </row>
     <row r="1860">
@@ -32154,13 +32154,13 @@
       </c>
       <c r="B1860" t="inlineStr"/>
       <c r="C1860" t="n">
-        <v>-39.1231689453125</v>
+        <v>15.7839994430542</v>
       </c>
       <c r="D1860" t="n">
-        <v>-37.74115371704102</v>
+        <v>18.41250801086426</v>
       </c>
       <c r="E1860" t="n">
-        <v>-37.02981948852539</v>
+        <v>19.76542472839355</v>
       </c>
     </row>
     <row r="1861">
@@ -32171,13 +32171,13 @@
       </c>
       <c r="B1861" t="inlineStr"/>
       <c r="C1861" t="n">
-        <v>-19.10225677490234</v>
+        <v>45.08815002441406</v>
       </c>
       <c r="D1861" t="n">
-        <v>-21.7111930847168</v>
+        <v>40.40908813476562</v>
       </c>
       <c r="E1861" t="n">
-        <v>-21.29512786865234</v>
+        <v>41.15528869628906</v>
       </c>
     </row>
     <row r="1862">
@@ -32188,13 +32188,13 @@
       </c>
       <c r="B1862" t="inlineStr"/>
       <c r="C1862" t="n">
-        <v>249.8621673583984</v>
+        <v>551.9282836914062</v>
       </c>
       <c r="D1862" t="n">
-        <v>265.9898376464844</v>
+        <v>581.9803466796875</v>
       </c>
       <c r="E1862" t="n">
-        <v>277.5034484863281</v>
+        <v>603.4346313476562</v>
       </c>
     </row>
     <row r="1863">
@@ -32206,13 +32206,13 @@
       </c>
       <c r="B1863" t="inlineStr"/>
       <c r="C1863" t="n">
-        <v>-21.96667289733887</v>
+        <v>48.09910202026367</v>
       </c>
       <c r="D1863" t="n">
-        <v>-20.1750545501709</v>
+        <v>51.49940872192383</v>
       </c>
       <c r="E1863" t="n">
-        <v>-16.58968353271484</v>
+        <v>58.30406951904297</v>
       </c>
     </row>
     <row r="1864">
@@ -32223,13 +32223,13 @@
       </c>
       <c r="B1864" t="inlineStr"/>
       <c r="C1864" t="n">
-        <v>-47.37667083740234</v>
+        <v>0.5567472577095032</v>
       </c>
       <c r="D1864" t="n">
-        <v>-47.38815689086914</v>
+        <v>0.5347962975502014</v>
       </c>
       <c r="E1864" t="n">
-        <v>-47.36852645874023</v>
+        <v>0.5723039507865906</v>
       </c>
     </row>
     <row r="1865">
@@ -32240,13 +32240,13 @@
       </c>
       <c r="B1865" t="inlineStr"/>
       <c r="C1865" t="n">
-        <v>-40.28091812133789</v>
+        <v>11.66408443450928</v>
       </c>
       <c r="D1865" t="n">
-        <v>-37.78383255004883</v>
+        <v>16.33318519592285</v>
       </c>
       <c r="E1865" t="n">
-        <v>-36.80512619018555</v>
+        <v>18.1631965637207</v>
       </c>
     </row>
     <row r="1866">
@@ -32257,13 +32257,13 @@
       </c>
       <c r="B1866" t="inlineStr"/>
       <c r="C1866" t="n">
-        <v>4.346621036529541</v>
+        <v>83.26934051513672</v>
       </c>
       <c r="D1866" t="n">
-        <v>-2.224188327789307</v>
+        <v>71.72869110107422</v>
       </c>
       <c r="E1866" t="n">
-        <v>-2.715710639953613</v>
+        <v>70.86540222167969</v>
       </c>
     </row>
     <row r="1867">
@@ -32274,13 +32274,13 @@
       </c>
       <c r="B1867" t="inlineStr"/>
       <c r="C1867" t="n">
-        <v>-40.4150276184082</v>
+        <v>8.32614803314209</v>
       </c>
       <c r="D1867" t="n">
-        <v>-37.54662322998047</v>
+        <v>13.54094219207764</v>
       </c>
       <c r="E1867" t="n">
-        <v>-37.14566040039062</v>
+        <v>14.26989555358887</v>
       </c>
     </row>
     <row r="1868">
@@ -32291,13 +32291,13 @@
       </c>
       <c r="B1868" t="inlineStr"/>
       <c r="C1868" t="n">
-        <v>-27.35002708435059</v>
+        <v>36.33148193359375</v>
       </c>
       <c r="D1868" t="n">
-        <v>-27.77956199645996</v>
+        <v>35.52544021606445</v>
       </c>
       <c r="E1868" t="n">
-        <v>-26.5982551574707</v>
+        <v>37.74222183227539</v>
       </c>
     </row>
     <row r="1869">
